--- a/other/calculations.xlsx
+++ b/other/calculations.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Data\C\_msvc_\spellcross-map-edit\other\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE41DA2E-5D07-4FA6-953F-FEAC711ADD9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="10965" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17790" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="geometry" sheetId="1" r:id="rId1"/>
@@ -17,7 +18,7 @@
     <sheet name="List1" sheetId="3" r:id="rId3"/>
     <sheet name="exp" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="57">
   <si>
     <t>y</t>
   </si>
@@ -178,11 +179,32 @@
   <si>
     <t>a</t>
   </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>xp</t>
+  </si>
+  <si>
+    <t>next xp</t>
+  </si>
+  <si>
+    <t>min XP</t>
+  </si>
+  <si>
+    <t>max XP</t>
+  </si>
+  <si>
+    <t>xpa</t>
+  </si>
+  <si>
+    <t>xpb</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -213,9 +235,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -234,7 +257,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="cs-CZ"/>
   <c:roundedCorners val="0"/>
@@ -248,7 +271,6 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -450,6 +472,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B744-4F3F-8EB1-7F6301A71368}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -567,6 +594,11 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-B744-4F3F-8EB1-7F6301A71368}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -751,7 +783,568 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="cs-CZ"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="cs-CZ"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.46209170361877128"/>
+                  <c:y val="-5.8673902420619088E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="cs-CZ"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>exp!$A$45:$A$55</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>exp!$J$45:$J$55</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.3274733159924657E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.3075612162525784E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.2743743833527667E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.1622791281729303</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.25168176518073371</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.3609292313211947</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.49006637366579964</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.6390707686788053</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.80791999282446858</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.99663646963853258</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6050-4990-8A78-FC2FC675A881}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>exp!$A$59:$A$69</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>exp!$J$59:$J$69</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.4167382370268371E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.3914626615656517E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.3486269137677713E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.16289650571025005</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.25212404267249638</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.36119017368529388</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.49008070297472445</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.63880982631470606</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.80735625004436185</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.99574126782456862</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-6050-4990-8A78-FC2FC675A881}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="784130152"/>
+        <c:axId val="784130512"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="784130152"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="cs-CZ"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="784130512"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="784130512"/>
+        <c:scaling>
+          <c:logBase val="10"/>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="cs-CZ"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="784130152"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="cs-CZ"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1307,24 +1900,546 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>509587</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>119062</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
+      <xdr:col>29</xdr:col>
       <xdr:colOff>204787</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>4762</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Graf 1"/>
+        <xdr:cNvPr id="2" name="Graf 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1334,6 +2449,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>304799</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>23811</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>9524</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>142874</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Graf 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D62A7D31-D1C0-24CD-1268-BAFF67C5A7FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1604,7 +2755,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1706,7 +2857,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -2120,7 +3271,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2317,19 +3468,22 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O41"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:V112"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.5703125" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2339,15 +3493,16 @@
       <c r="C2">
         <v>520</v>
       </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
         <f>C2/A2^2.5</f>
         <v>520</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="1"/>
+      <c r="L2">
         <v>520</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2357,15 +3512,16 @@
       <c r="C3">
         <v>3188</v>
       </c>
-      <c r="H3" s="1">
-        <f t="shared" ref="H3:H13" si="0">C3/A3^2.5</f>
+      <c r="I3" s="1">
+        <f t="shared" ref="I3:I13" si="0">C3/A3^2.5</f>
         <v>563.56410460567838</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="1"/>
+      <c r="L3">
         <v>1380</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2375,12 +3531,13 @@
       <c r="C4">
         <v>9632</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <f t="shared" si="0"/>
         <v>617.89308809271927</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2390,12 +3547,13 @@
       <c r="C5">
         <v>20373</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <f t="shared" si="0"/>
         <v>636.65625</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2405,12 +3563,13 @@
       <c r="C6">
         <v>35410</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <f t="shared" si="0"/>
         <v>633.43333666614046</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2420,12 +3579,13 @@
       <c r="C7">
         <v>54743</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <f t="shared" si="0"/>
         <v>620.79822680175721</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2435,12 +3595,13 @@
       <c r="C8">
         <v>78372</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <f t="shared" si="0"/>
         <v>604.5271771159014</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2450,12 +3611,13 @@
       <c r="C9">
         <v>106298</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <f t="shared" si="0"/>
         <v>587.2190361450597</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2465,12 +3627,13 @@
       <c r="C10">
         <v>138520</v>
       </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
         <f t="shared" si="0"/>
         <v>570.0411522633741</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2480,12 +3643,13 @@
       <c r="C11">
         <v>175038</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <f t="shared" si="0"/>
         <v>553.51875708055229</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2495,12 +3659,13 @@
       <c r="C12">
         <v>215852</v>
       </c>
-      <c r="H12" s="1">
+      <c r="I12" s="1">
         <f t="shared" si="0"/>
         <v>537.86633677520183</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2508,272 +3673,285 @@
         <v>221564</v>
       </c>
       <c r="C13">
-        <f>200*J3</f>
+        <f>200*L3</f>
         <v>276000</v>
       </c>
-      <c r="H13" s="1">
+      <c r="I13" s="1">
         <f t="shared" si="0"/>
         <v>553.29400797339144</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J13" s="1"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1</v>
       </c>
       <c r="C16">
         <v>1200</v>
       </c>
-      <c r="H16" s="1">
+      <c r="I16" s="1">
         <f>C16/A16^2.5</f>
         <v>1200</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="1"/>
+      <c r="L16">
         <v>1200</v>
       </c>
-      <c r="K16" s="1">
-        <f>$L$16*A16^2.5</f>
+      <c r="M16" s="1">
+        <f>$N$16*A16^2.5</f>
         <v>150</v>
       </c>
-      <c r="L16">
+      <c r="N16">
         <v>150</v>
       </c>
-      <c r="M16">
-        <f>K16/A16^2.5</f>
+      <c r="O16">
+        <f>M16/A16^2.5</f>
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2</v>
       </c>
       <c r="C17">
         <v>7225</v>
       </c>
-      <c r="H17" s="1">
-        <f t="shared" ref="H17:H27" si="1">C17/A17^2.5</f>
+      <c r="I17" s="1">
+        <f t="shared" ref="I17:I26" si="1">C17/A17^2.5</f>
         <v>1277.2116235182013</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="1"/>
+      <c r="L17">
         <v>3100</v>
       </c>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K27" si="2">$L$16*A17^2.5</f>
+      <c r="M17" s="1">
+        <f t="shared" ref="M17:M27" si="2">$N$16*A17^2.5</f>
         <v>848.52813742385706</v>
       </c>
-      <c r="L17">
+      <c r="N17">
         <v>130</v>
       </c>
-      <c r="M17">
-        <f t="shared" ref="M17:M27" si="3">K17/A17^2.5</f>
+      <c r="O17">
+        <f t="shared" ref="O17:O27" si="3">M17/A17^2.5</f>
         <v>150</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>3</v>
       </c>
       <c r="C18">
         <v>21700</v>
       </c>
-      <c r="H18" s="1">
+      <c r="I18" s="1">
         <f t="shared" si="1"/>
         <v>1392.0556490460972</v>
       </c>
-      <c r="K18" s="1">
+      <c r="J18" s="1"/>
+      <c r="M18" s="1">
         <f t="shared" si="2"/>
         <v>2338.2685902179851</v>
       </c>
-      <c r="M18">
+      <c r="O18">
         <f t="shared" si="3"/>
         <v>150</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>4</v>
       </c>
       <c r="C19">
         <v>45825</v>
       </c>
-      <c r="H19" s="1">
+      <c r="I19" s="1">
         <f t="shared" si="1"/>
         <v>1432.03125</v>
       </c>
-      <c r="K19" s="1">
+      <c r="J19" s="1"/>
+      <c r="M19" s="1">
         <f t="shared" si="2"/>
         <v>4800</v>
       </c>
-      <c r="M19">
+      <c r="O19">
         <f t="shared" si="3"/>
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>5</v>
       </c>
       <c r="C20">
         <v>79600</v>
       </c>
-      <c r="H20" s="1">
+      <c r="I20" s="1">
         <f t="shared" si="1"/>
         <v>1423.9280880718663</v>
       </c>
-      <c r="K20" s="1">
+      <c r="J20" s="1"/>
+      <c r="M20" s="1">
         <f t="shared" si="2"/>
         <v>8385.2549156242094</v>
       </c>
-      <c r="M20">
+      <c r="O20">
         <f t="shared" si="3"/>
         <v>150</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>6</v>
       </c>
       <c r="C21">
         <v>123025</v>
       </c>
-      <c r="H21" s="1">
+      <c r="I21" s="1">
         <f t="shared" si="1"/>
         <v>1395.131831508799</v>
       </c>
-      <c r="K21" s="1">
+      <c r="J21" s="1"/>
+      <c r="M21" s="1">
         <f t="shared" si="2"/>
         <v>13227.244611029157</v>
       </c>
-      <c r="M21">
+      <c r="O21">
         <f t="shared" si="3"/>
         <v>150</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>7</v>
       </c>
       <c r="C22">
         <v>176100</v>
       </c>
-      <c r="H22" s="1">
+      <c r="I22" s="1">
         <f t="shared" si="1"/>
         <v>1358.3580346311212</v>
       </c>
-      <c r="K22" s="1">
+      <c r="J22" s="1"/>
+      <c r="M22" s="1">
         <f t="shared" si="2"/>
         <v>19446.272136324733</v>
       </c>
-      <c r="M22">
+      <c r="O22">
         <f t="shared" si="3"/>
         <v>150</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>8</v>
       </c>
       <c r="C23">
         <v>238825</v>
       </c>
-      <c r="H23" s="1">
+      <c r="I23" s="1">
         <f t="shared" si="1"/>
         <v>1319.3341954443536</v>
       </c>
-      <c r="K23" s="1">
+      <c r="J23" s="1"/>
+      <c r="M23" s="1">
         <f t="shared" si="2"/>
         <v>27152.900397563419</v>
       </c>
-      <c r="M23">
+      <c r="O23">
         <f t="shared" si="3"/>
         <v>150</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9</v>
       </c>
       <c r="C24">
         <v>311200</v>
       </c>
-      <c r="H24" s="1">
+      <c r="I24" s="1">
         <f t="shared" si="1"/>
         <v>1280.6584362139909</v>
       </c>
-      <c r="K24" s="1">
+      <c r="J24" s="1"/>
+      <c r="M24" s="1">
         <f t="shared" si="2"/>
         <v>36450.000000000029</v>
       </c>
-      <c r="M24">
+      <c r="O24">
         <f t="shared" si="3"/>
         <v>150.00000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>10</v>
       </c>
       <c r="C25">
         <v>394225</v>
       </c>
-      <c r="H25" s="1">
+      <c r="I25" s="1">
         <f t="shared" si="1"/>
         <v>1246.648910579878</v>
       </c>
-      <c r="K25" s="1">
+      <c r="J25" s="1"/>
+      <c r="M25" s="1">
         <f t="shared" si="2"/>
         <v>47434.164902525736</v>
       </c>
-      <c r="M25">
+      <c r="O25">
         <f t="shared" si="3"/>
         <v>150</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>11</v>
       </c>
       <c r="C26">
         <v>484900</v>
       </c>
-      <c r="H26" s="1">
+      <c r="I26" s="1">
         <f t="shared" si="1"/>
         <v>1208.2880246756822</v>
       </c>
-      <c r="K26" s="1">
+      <c r="J26" s="1"/>
+      <c r="M26" s="1">
         <f t="shared" si="2"/>
         <v>60196.739944950525</v>
       </c>
-      <c r="M26">
+      <c r="O26">
         <f t="shared" si="3"/>
         <v>150</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>12</v>
       </c>
       <c r="C27">
-        <f>J17*200</f>
+        <f>L17*200</f>
         <v>620000</v>
       </c>
-      <c r="H27" s="1">
+      <c r="I27" s="1">
         <f>C27/A27^2.5</f>
         <v>1242.9068295054444</v>
       </c>
-      <c r="K27" s="1">
+      <c r="J27" s="1"/>
+      <c r="M27" s="1">
         <f t="shared" si="2"/>
         <v>74824.594886975494</v>
       </c>
-      <c r="L27">
-        <f>L17*200</f>
+      <c r="N27">
+        <f>N17*200</f>
         <v>26000</v>
       </c>
-      <c r="M27">
+      <c r="O27">
         <f t="shared" si="3"/>
         <v>150</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>1</v>
       </c>
@@ -2781,25 +3959,26 @@
         <v>150</v>
       </c>
       <c r="D30">
-        <f>$O$30*A30^$O$31</f>
+        <f>$Q$30*A30^$Q$31</f>
         <v>150</v>
       </c>
-      <c r="H30" s="1">
+      <c r="I30" s="1">
         <f>C30/A30^2.5</f>
         <v>150</v>
       </c>
-      <c r="J30">
+      <c r="J30" s="1"/>
+      <c r="L30">
         <v>150</v>
       </c>
-      <c r="N30" t="s">
+      <c r="P30" t="s">
         <v>49</v>
       </c>
-      <c r="O30">
-        <f>J30</f>
+      <c r="Q30">
+        <f>L30</f>
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2</v>
       </c>
@@ -2807,25 +3986,26 @@
         <v>500</v>
       </c>
       <c r="D31">
-        <f t="shared" ref="D31:D41" si="4">$O$30*A31^$O$31</f>
+        <f t="shared" ref="D31:D41" si="4">$Q$30*A31^$Q$31</f>
         <v>631.84655785531265</v>
       </c>
-      <c r="H31" s="1">
-        <f t="shared" ref="H31:H41" si="5">C31/A31^2.5</f>
+      <c r="I31" s="1">
+        <f t="shared" ref="I31:I41" si="5">C31/A31^2.5</f>
         <v>88.38834764831843</v>
       </c>
-      <c r="J31">
+      <c r="J31" s="1"/>
+      <c r="L31">
         <v>130</v>
       </c>
-      <c r="N31" t="s">
+      <c r="P31" t="s">
         <v>48</v>
       </c>
-      <c r="O31">
-        <f>LN(J31*200/J30)/LN(12)</f>
+      <c r="Q31">
+        <f>LN(L31*200/L30)/LN(12)</f>
         <v>2.0746117458163589</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>3</v>
       </c>
@@ -2836,12 +4016,13 @@
         <f t="shared" si="4"/>
         <v>1465.3204756903931</v>
       </c>
-      <c r="H32" s="1">
+      <c r="I32" s="1">
         <f t="shared" si="5"/>
         <v>70.75748299068411</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>4</v>
       </c>
@@ -2852,12 +4033,13 @@
         <f t="shared" si="4"/>
         <v>2661.5338178240459</v>
       </c>
-      <c r="H33" s="1">
+      <c r="I33" s="1">
         <f t="shared" si="5"/>
         <v>65.84375</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>5</v>
       </c>
@@ -2868,12 +4050,13 @@
         <f t="shared" si="4"/>
         <v>4228.464024802015</v>
       </c>
-      <c r="H34" s="1">
+      <c r="I34" s="1">
         <f t="shared" si="5"/>
         <v>62.824565895834098</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>6</v>
       </c>
@@ -2884,12 +4067,13 @@
         <f t="shared" si="4"/>
         <v>6172.384658132557</v>
       </c>
-      <c r="H35" s="1">
+      <c r="I35" s="1">
         <f t="shared" si="5"/>
         <v>60.318684916035785</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J35" s="1"/>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>7</v>
       </c>
@@ -2900,12 +4084,13 @@
         <f t="shared" si="4"/>
         <v>8498.4863115812968</v>
       </c>
-      <c r="H36" s="1">
+      <c r="I36" s="1">
         <f t="shared" si="5"/>
         <v>58.067684751295182</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J36" s="1"/>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>8</v>
       </c>
@@ -2916,12 +4101,13 @@
         <f t="shared" si="4"/>
         <v>11211.206542717537</v>
       </c>
-      <c r="H37" s="1">
+      <c r="I37" s="1">
         <f t="shared" si="5"/>
         <v>56.005066778665785</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J37" s="1"/>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>9</v>
       </c>
@@ -2932,12 +4118,13 @@
         <f t="shared" si="4"/>
         <v>14314.427309850129</v>
       </c>
-      <c r="H38" s="1">
+      <c r="I38" s="1">
         <f t="shared" si="5"/>
         <v>54.115226337448519</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J38" s="1"/>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>10</v>
       </c>
@@ -2948,12 +4135,13 @@
         <f t="shared" si="4"/>
         <v>17811.60292724118</v>
       </c>
-      <c r="H39" s="1">
+      <c r="I39" s="1">
         <f t="shared" si="5"/>
         <v>52.376804885368813</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J39" s="1"/>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>11</v>
       </c>
@@ -2964,30 +4152,3151 @@
         <f t="shared" si="4"/>
         <v>21705.847912566867</v>
       </c>
-      <c r="H40" s="1">
+      <c r="I40" s="1">
         <f t="shared" si="5"/>
         <v>50.778497353765829</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J40" s="1"/>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>12</v>
       </c>
       <c r="C41">
-        <f>J31*200</f>
+        <f>L31*200</f>
         <v>26000</v>
       </c>
       <c r="D41">
         <f t="shared" si="4"/>
         <v>25999.999999999989</v>
       </c>
-      <c r="H41" s="1">
+      <c r="I41" s="1">
         <f t="shared" si="5"/>
         <v>52.121899301841218</v>
       </c>
+      <c r="J41" s="1"/>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" t="s">
+        <v>51</v>
+      </c>
+      <c r="D44" t="s">
+        <v>52</v>
+      </c>
+      <c r="L44" t="s">
+        <v>53</v>
+      </c>
+      <c r="M44">
+        <v>150</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>1</v>
+      </c>
+      <c r="R44" t="s">
+        <v>0</v>
+      </c>
+      <c r="S44" t="s">
+        <v>55</v>
+      </c>
+      <c r="T44" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>1</v>
+      </c>
+      <c r="B45">
+        <f>LOG10(A45)</f>
+        <v>0</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>150</v>
+      </c>
+      <c r="E45">
+        <f>D45/$D$55</f>
+        <v>3.3635303614673964E-3</v>
+      </c>
+      <c r="F45">
+        <f>LOG10(D45)</f>
+        <v>2.1760912590556813</v>
+      </c>
+      <c r="G45">
+        <f>(D45-$M$44)/$M$45</f>
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <f>D45/$M$45</f>
+        <v>5.263157894736842E-3</v>
+      </c>
+      <c r="J45">
+        <f>(D45-$D$45)/$D$55</f>
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <f>$M$44+G45*$M$45</f>
+        <v>150</v>
+      </c>
+      <c r="L45" t="s">
+        <v>54</v>
+      </c>
+      <c r="M45">
+        <v>28500</v>
+      </c>
+      <c r="N45">
+        <f>M45/M44</f>
+        <v>190</v>
+      </c>
+      <c r="O45" s="1">
+        <f>$M$44*A45^$M$48</f>
+        <v>150</v>
+      </c>
+      <c r="P45" s="2"/>
+      <c r="Q45">
+        <f>A45</f>
+        <v>1</v>
+      </c>
+      <c r="R45">
+        <f>D45</f>
+        <v>150</v>
+      </c>
+      <c r="S45">
+        <f>M44</f>
+        <v>150</v>
+      </c>
+      <c r="T45" s="1">
+        <f>M45</f>
+        <v>28500</v>
+      </c>
+      <c r="U45" s="1">
+        <f>R45</f>
+        <v>150</v>
+      </c>
+      <c r="V45" s="2">
+        <f>U45-R45</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>2</v>
+      </c>
+      <c r="B46">
+        <f t="shared" ref="B46:B56" si="6">LOG10(A46)</f>
+        <v>0.3010299956639812</v>
+      </c>
+      <c r="D46">
+        <v>742</v>
+      </c>
+      <c r="E46">
+        <f t="shared" ref="E46:E56" si="7">D46/$D$55</f>
+        <v>1.6638263521392051E-2</v>
+      </c>
+      <c r="F46">
+        <f t="shared" ref="F46:F56" si="8">LOG10(D46)</f>
+        <v>2.8704039052790269</v>
+      </c>
+      <c r="G46">
+        <f>(D46-$M$44)/$M$45</f>
+        <v>2.0771929824561403E-2</v>
+      </c>
+      <c r="H46">
+        <f t="shared" ref="H46:H56" si="9">D46/$M$45</f>
+        <v>2.6035087719298244E-2</v>
+      </c>
+      <c r="J46">
+        <f t="shared" ref="J46:J56" si="10">(D46-$D$45)/$D$55</f>
+        <v>1.3274733159924657E-2</v>
+      </c>
+      <c r="K46">
+        <f>$M$44+G46*$M$45</f>
+        <v>742</v>
+      </c>
+      <c r="O46" s="1">
+        <f t="shared" ref="O46:O56" si="11">$M$44*A46^$M$48</f>
+        <v>775.41169838249539</v>
+      </c>
+      <c r="P46" s="2"/>
+      <c r="Q46">
+        <f t="shared" ref="Q46:Q56" si="12">A46</f>
+        <v>2</v>
+      </c>
+      <c r="R46">
+        <f t="shared" ref="R46:R55" si="13">D46</f>
+        <v>742</v>
+      </c>
+      <c r="T46" s="1"/>
+      <c r="U46" s="1">
+        <f t="shared" ref="U46:U56" si="14">ROUNDDOWN(2*$S$45+(Q46-1)^2/64*($T$45-$S$45),0)</f>
+        <v>742</v>
+      </c>
+      <c r="V46" s="2">
+        <f t="shared" ref="V46:V56" si="15">U46-R46</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>3</v>
+      </c>
+      <c r="B47">
+        <f t="shared" si="6"/>
+        <v>0.47712125471966244</v>
+      </c>
+      <c r="D47">
+        <v>2071</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="7"/>
+        <v>4.6439142523993185E-2</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="8"/>
+        <v>3.3161800988934527</v>
+      </c>
+      <c r="G47">
+        <f>(D47-$M$44)/$M$45</f>
+        <v>6.7403508771929826E-2</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="9"/>
+        <v>7.2666666666666671E-2</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="10"/>
+        <v>4.3075612162525784E-2</v>
+      </c>
+      <c r="K47">
+        <f>$M$44+G47*$M$45</f>
+        <v>2071</v>
+      </c>
+      <c r="O47" s="1">
+        <f t="shared" si="11"/>
+        <v>2027.0694701040443</v>
+      </c>
+      <c r="P47" s="2"/>
+      <c r="Q47">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="R47">
+        <f t="shared" si="13"/>
+        <v>2071</v>
+      </c>
+      <c r="T47" s="1"/>
+      <c r="U47" s="1">
+        <f t="shared" si="14"/>
+        <v>2071</v>
+      </c>
+      <c r="V47" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>4</v>
+      </c>
+      <c r="B48">
+        <f t="shared" si="6"/>
+        <v>0.6020599913279624</v>
+      </c>
+      <c r="D48">
+        <v>4286</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="7"/>
+        <v>9.6107274194995068E-2</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="8"/>
+        <v>3.6320521667058099</v>
+      </c>
+      <c r="G48">
+        <f>(D48-$M$44)/$M$45</f>
+        <v>0.14512280701754385</v>
+      </c>
+      <c r="H48">
+        <f t="shared" si="9"/>
+        <v>0.15038596491228071</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="10"/>
+        <v>9.2743743833527667E-2</v>
+      </c>
+      <c r="K48">
+        <f>$M$44+G48*$M$45</f>
+        <v>4286</v>
+      </c>
+      <c r="L48" t="s">
+        <v>49</v>
+      </c>
+      <c r="M48">
+        <v>2.37</v>
+      </c>
+      <c r="O48" s="1">
+        <f t="shared" si="11"/>
+        <v>4008.4220132561736</v>
+      </c>
+      <c r="P48" s="2"/>
+      <c r="Q48">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="R48">
+        <f t="shared" si="13"/>
+        <v>4286</v>
+      </c>
+      <c r="T48" s="1"/>
+      <c r="U48" s="1">
+        <f t="shared" si="14"/>
+        <v>4286</v>
+      </c>
+      <c r="V48" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>5</v>
+      </c>
+      <c r="B49">
+        <f t="shared" si="6"/>
+        <v>0.69897000433601886</v>
+      </c>
+      <c r="D49">
+        <v>7387</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="7"/>
+        <v>0.16564265853439769</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="8"/>
+        <v>3.8684680990209865</v>
+      </c>
+      <c r="G49">
+        <f>(D49-$M$44)/$M$45</f>
+        <v>0.25392982456140351</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="9"/>
+        <v>0.25919298245614036</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="10"/>
+        <v>0.1622791281729303</v>
+      </c>
+      <c r="K49">
+        <f>$M$44+G49*$M$45</f>
+        <v>7387</v>
+      </c>
+      <c r="O49" s="1">
+        <f t="shared" si="11"/>
+        <v>6802.2120964546129</v>
+      </c>
+      <c r="P49" s="2"/>
+      <c r="Q49">
+        <f t="shared" si="12"/>
+        <v>5</v>
+      </c>
+      <c r="R49">
+        <f t="shared" si="13"/>
+        <v>7387</v>
+      </c>
+      <c r="T49" s="1"/>
+      <c r="U49" s="1">
+        <f t="shared" si="14"/>
+        <v>7387</v>
+      </c>
+      <c r="V49" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>6</v>
+      </c>
+      <c r="B50">
+        <f t="shared" si="6"/>
+        <v>0.77815125038364363</v>
+      </c>
+      <c r="D50">
+        <v>11374</v>
+      </c>
+      <c r="E50">
+        <f t="shared" si="7"/>
+        <v>0.25504529554220107</v>
+      </c>
+      <c r="F50">
+        <f t="shared" si="8"/>
+        <v>4.0559132239161491</v>
+      </c>
+      <c r="G50">
+        <f>(D50-$M$44)/$M$45</f>
+        <v>0.3938245614035088</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="9"/>
+        <v>0.3990877192982456</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="10"/>
+        <v>0.25168176518073371</v>
+      </c>
+      <c r="K50">
+        <f>$M$44+G50*$M$45</f>
+        <v>11374</v>
+      </c>
+      <c r="O50" s="1">
+        <f t="shared" si="11"/>
+        <v>10478.755870351211</v>
+      </c>
+      <c r="P50" s="2"/>
+      <c r="Q50">
+        <f t="shared" si="12"/>
+        <v>6</v>
+      </c>
+      <c r="R50">
+        <f t="shared" si="13"/>
+        <v>11374</v>
+      </c>
+      <c r="T50" s="1"/>
+      <c r="U50" s="1">
+        <f t="shared" si="14"/>
+        <v>11374</v>
+      </c>
+      <c r="V50" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>7</v>
+      </c>
+      <c r="B51">
+        <f t="shared" si="6"/>
+        <v>0.84509804001425681</v>
+      </c>
+      <c r="D51">
+        <v>16246</v>
+      </c>
+      <c r="E51">
+        <f t="shared" si="7"/>
+        <v>0.36429276168266211</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="8"/>
+        <v>4.2107464488983259</v>
+      </c>
+      <c r="G51">
+        <f>(D51-$M$44)/$M$45</f>
+        <v>0.56477192982456137</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="9"/>
+        <v>0.57003508771929823</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="10"/>
+        <v>0.3609292313211947</v>
+      </c>
+      <c r="K51">
+        <f>$M$44+G51*$M$45</f>
+        <v>16245.999999999998</v>
+      </c>
+      <c r="O51" s="1">
+        <f t="shared" si="11"/>
+        <v>15099.884101215204</v>
+      </c>
+      <c r="P51" s="2"/>
+      <c r="Q51">
+        <f t="shared" si="12"/>
+        <v>7</v>
+      </c>
+      <c r="R51">
+        <f t="shared" si="13"/>
+        <v>16246</v>
+      </c>
+      <c r="T51" s="1"/>
+      <c r="U51" s="1">
+        <f t="shared" si="14"/>
+        <v>16246</v>
+      </c>
+      <c r="V51" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>8</v>
+      </c>
+      <c r="B52">
+        <f t="shared" si="6"/>
+        <v>0.90308998699194354</v>
+      </c>
+      <c r="D52">
+        <v>22005</v>
+      </c>
+      <c r="E52">
+        <f t="shared" si="7"/>
+        <v>0.493429904027267</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="8"/>
+        <v>4.3425213728989638</v>
+      </c>
+      <c r="G52">
+        <f>(D52-$M$44)/$M$45</f>
+        <v>0.76684210526315788</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="9"/>
+        <v>0.77210526315789474</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="10"/>
+        <v>0.49006637366579964</v>
+      </c>
+      <c r="K52">
+        <f>$M$44+G52*$M$45</f>
+        <v>22005</v>
+      </c>
+      <c r="O52" s="1">
+        <f t="shared" si="11"/>
+        <v>20721.182140885001</v>
+      </c>
+      <c r="P52" s="2"/>
+      <c r="Q52">
+        <f t="shared" si="12"/>
+        <v>8</v>
+      </c>
+      <c r="R52">
+        <f t="shared" si="13"/>
+        <v>22005</v>
+      </c>
+      <c r="T52" s="1"/>
+      <c r="U52" s="1">
+        <f t="shared" si="14"/>
+        <v>22005</v>
+      </c>
+      <c r="V52" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>9</v>
+      </c>
+      <c r="B53">
+        <f t="shared" si="6"/>
+        <v>0.95424250943932487</v>
+      </c>
+      <c r="D53">
+        <v>28650</v>
+      </c>
+      <c r="E53">
+        <f t="shared" si="7"/>
+        <v>0.64243429904027272</v>
+      </c>
+      <c r="F53">
+        <f t="shared" si="8"/>
+        <v>4.4571246263034086</v>
+      </c>
+      <c r="G53">
+        <f>(D53-$M$44)/$M$45</f>
+        <v>1</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="9"/>
+        <v>1.0052631578947369</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="10"/>
+        <v>0.6390707686788053</v>
+      </c>
+      <c r="K53">
+        <f>$M$44+G53*$M$45</f>
+        <v>28650</v>
+      </c>
+      <c r="O53" s="1">
+        <f t="shared" si="11"/>
+        <v>27393.404244185942</v>
+      </c>
+      <c r="P53" s="2"/>
+      <c r="Q53">
+        <f t="shared" si="12"/>
+        <v>9</v>
+      </c>
+      <c r="R53">
+        <f t="shared" si="13"/>
+        <v>28650</v>
+      </c>
+      <c r="T53" s="1"/>
+      <c r="U53" s="1">
+        <f t="shared" si="14"/>
+        <v>28650</v>
+      </c>
+      <c r="V53" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>10</v>
+      </c>
+      <c r="B54">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="D54">
+        <v>36180</v>
+      </c>
+      <c r="E54">
+        <f t="shared" si="7"/>
+        <v>0.811283523185936</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="8"/>
+        <v>4.5584685625237951</v>
+      </c>
+      <c r="G54">
+        <f>(D54-$M$44)/$M$45</f>
+        <v>1.2642105263157895</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="9"/>
+        <v>1.2694736842105263</v>
+      </c>
+      <c r="J54">
+        <f t="shared" si="10"/>
+        <v>0.80791999282446858</v>
+      </c>
+      <c r="K54">
+        <f>$M$44+G54*$M$45</f>
+        <v>36180</v>
+      </c>
+      <c r="O54" s="1">
+        <f t="shared" si="11"/>
+        <v>35163.432229798847</v>
+      </c>
+      <c r="P54" s="2"/>
+      <c r="Q54">
+        <f t="shared" si="12"/>
+        <v>10</v>
+      </c>
+      <c r="R54">
+        <f t="shared" si="13"/>
+        <v>36180</v>
+      </c>
+      <c r="T54" s="1"/>
+      <c r="U54" s="1">
+        <f t="shared" si="14"/>
+        <v>36180</v>
+      </c>
+      <c r="V54" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>11</v>
+      </c>
+      <c r="B55">
+        <f t="shared" si="6"/>
+        <v>1.0413926851582251</v>
+      </c>
+      <c r="D55">
+        <v>44596</v>
+      </c>
+      <c r="E55">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="8"/>
+        <v>4.6492959067876436</v>
+      </c>
+      <c r="G55">
+        <f>(D55-$M$44)/$M$45</f>
+        <v>1.5595087719298246</v>
+      </c>
+      <c r="H55">
+        <f t="shared" si="9"/>
+        <v>1.5647719298245615</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="10"/>
+        <v>0.99663646963853258</v>
+      </c>
+      <c r="K55">
+        <f>$M$44+G55*$M$45</f>
+        <v>44596</v>
+      </c>
+      <c r="O55" s="1">
+        <f t="shared" si="11"/>
+        <v>44074.959599212918</v>
+      </c>
+      <c r="P55" s="2"/>
+      <c r="Q55">
+        <f t="shared" si="12"/>
+        <v>11</v>
+      </c>
+      <c r="R55">
+        <f t="shared" si="13"/>
+        <v>44596</v>
+      </c>
+      <c r="T55" s="1"/>
+      <c r="U55" s="1">
+        <f t="shared" si="14"/>
+        <v>44596</v>
+      </c>
+      <c r="V55" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>12</v>
+      </c>
+      <c r="B56">
+        <f t="shared" si="6"/>
+        <v>1.0791812460476249</v>
+      </c>
+      <c r="D56">
+        <f>2*M45</f>
+        <v>57000</v>
+      </c>
+      <c r="E56">
+        <f t="shared" si="7"/>
+        <v>1.2781415373576106</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="8"/>
+        <v>4.7558748556724915</v>
+      </c>
+      <c r="G56">
+        <f>(D56-$M$44)/$M$45</f>
+        <v>1.9947368421052631</v>
+      </c>
+      <c r="H56">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="J56">
+        <f t="shared" si="10"/>
+        <v>1.2747780069961432</v>
+      </c>
+      <c r="K56">
+        <f>$M$44+G56*$M$45</f>
+        <v>57000</v>
+      </c>
+      <c r="O56" s="1">
+        <f t="shared" si="11"/>
+        <v>54168.999242430524</v>
+      </c>
+      <c r="P56" s="2"/>
+      <c r="Q56">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="T56" s="1"/>
+      <c r="U56" s="1">
+        <f t="shared" si="14"/>
+        <v>53899</v>
+      </c>
+      <c r="V56" s="2">
+        <f t="shared" si="15"/>
+        <v>53899</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" t="s">
+        <v>51</v>
+      </c>
+      <c r="D58" t="s">
+        <v>52</v>
+      </c>
+      <c r="L58" t="s">
+        <v>53</v>
+      </c>
+      <c r="M58">
+        <v>600</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>1</v>
+      </c>
+      <c r="R58" t="s">
+        <v>0</v>
+      </c>
+      <c r="S58" t="s">
+        <v>55</v>
+      </c>
+      <c r="T58" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>1</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>600</v>
+      </c>
+      <c r="F59">
+        <f>LOG10(D59)</f>
+        <v>2.7781512503836434</v>
+      </c>
+      <c r="G59">
+        <f>(D59-$M$58)/$M$59</f>
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <f>D59/$M$59</f>
+        <v>6.6666666666666671E-3</v>
+      </c>
+      <c r="J59">
+        <f>(D59-$D$59)/$D$69</f>
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <f>$M$58+G59*$M$59</f>
+        <v>600</v>
+      </c>
+      <c r="L59" t="s">
+        <v>54</v>
+      </c>
+      <c r="M59">
+        <v>90000</v>
+      </c>
+      <c r="N59">
+        <f>M59/M58</f>
+        <v>150</v>
+      </c>
+      <c r="Q59">
+        <f>A59</f>
+        <v>1</v>
+      </c>
+      <c r="R59">
+        <f>D59</f>
+        <v>600</v>
+      </c>
+      <c r="S59">
+        <f>M58</f>
+        <v>600</v>
+      </c>
+      <c r="T59" s="1">
+        <f>M59</f>
+        <v>90000</v>
+      </c>
+      <c r="U59" s="1">
+        <f>R59</f>
+        <v>600</v>
+      </c>
+      <c r="V59" s="2">
+        <f>U59-R59</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>2</v>
+      </c>
+      <c r="D60">
+        <v>2596</v>
+      </c>
+      <c r="E60">
+        <f>D60/$D$59</f>
+        <v>4.3266666666666671</v>
+      </c>
+      <c r="F60">
+        <f t="shared" ref="F60:F70" si="16">LOG10(D60)</f>
+        <v>3.4143046881283317</v>
+      </c>
+      <c r="G60">
+        <f>(D60-$M$58)/$M$59</f>
+        <v>2.2177777777777779E-2</v>
+      </c>
+      <c r="H60">
+        <f t="shared" ref="H60:H70" si="17">D60/$M$59</f>
+        <v>2.8844444444444443E-2</v>
+      </c>
+      <c r="J60">
+        <f t="shared" ref="J60:J70" si="18">(D60-$D$59)/$D$69</f>
+        <v>1.4167382370268371E-2</v>
+      </c>
+      <c r="K60">
+        <f t="shared" ref="K60:K70" si="19">$M$58+G60*$M$59</f>
+        <v>2596</v>
+      </c>
+      <c r="Q60">
+        <f t="shared" ref="Q60:Q70" si="20">A60</f>
+        <v>2</v>
+      </c>
+      <c r="R60">
+        <f t="shared" ref="R60:R69" si="21">D60</f>
+        <v>2596</v>
+      </c>
+      <c r="T60" s="1"/>
+      <c r="U60" s="1">
+        <f>ROUNDDOWN(2*$S$59+(Q60-1)^2/64*($T$59-$S$59),0)</f>
+        <v>2596</v>
+      </c>
+      <c r="V60" s="2">
+        <f t="shared" ref="V60:V70" si="22">U60-R60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>3</v>
+      </c>
+      <c r="D61">
+        <v>6787</v>
+      </c>
+      <c r="E61">
+        <f t="shared" ref="E61:E70" si="23">D61/$D$59</f>
+        <v>11.311666666666667</v>
+      </c>
+      <c r="F61">
+        <f t="shared" si="16"/>
+        <v>3.8316778491914669</v>
+      </c>
+      <c r="G61">
+        <f>(D61-$M$58)/$M$59</f>
+        <v>6.8744444444444441E-2</v>
+      </c>
+      <c r="H61">
+        <f t="shared" si="17"/>
+        <v>7.5411111111111109E-2</v>
+      </c>
+      <c r="J61">
+        <f t="shared" si="18"/>
+        <v>4.3914626615656517E-2</v>
+      </c>
+      <c r="K61">
+        <f t="shared" si="19"/>
+        <v>6787</v>
+      </c>
+      <c r="Q61">
+        <f t="shared" si="20"/>
+        <v>3</v>
+      </c>
+      <c r="R61">
+        <f t="shared" si="21"/>
+        <v>6787</v>
+      </c>
+      <c r="T61" s="1"/>
+      <c r="U61" s="1">
+        <f t="shared" ref="U61:U70" si="24">ROUNDDOWN(2*$S$59+(Q61-1)^2/64*($T$59-$S$59),0)</f>
+        <v>6787</v>
+      </c>
+      <c r="V61" s="2">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>4</v>
+      </c>
+      <c r="D62">
+        <v>13771</v>
+      </c>
+      <c r="E62">
+        <f t="shared" si="23"/>
+        <v>22.951666666666668</v>
+      </c>
+      <c r="F62">
+        <f t="shared" si="16"/>
+        <v>4.1389654782898271</v>
+      </c>
+      <c r="G62">
+        <f>(D62-$M$58)/$M$59</f>
+        <v>0.14634444444444444</v>
+      </c>
+      <c r="H62">
+        <f t="shared" si="17"/>
+        <v>0.1530111111111111</v>
+      </c>
+      <c r="J62">
+        <f t="shared" si="18"/>
+        <v>9.3486269137677713E-2</v>
+      </c>
+      <c r="K62">
+        <f t="shared" si="19"/>
+        <v>13771</v>
+      </c>
+      <c r="Q62">
+        <f t="shared" si="20"/>
+        <v>4</v>
+      </c>
+      <c r="R62">
+        <f t="shared" si="21"/>
+        <v>13771</v>
+      </c>
+      <c r="T62" s="1"/>
+      <c r="U62" s="1">
+        <f t="shared" si="24"/>
+        <v>13771</v>
+      </c>
+      <c r="V62" s="2">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>5</v>
+      </c>
+      <c r="D63">
+        <v>23550</v>
+      </c>
+      <c r="E63">
+        <f t="shared" si="23"/>
+        <v>39.25</v>
+      </c>
+      <c r="F63">
+        <f t="shared" si="16"/>
+        <v>4.3719909114649154</v>
+      </c>
+      <c r="G63">
+        <f>(D63-$M$58)/$M$59</f>
+        <v>0.255</v>
+      </c>
+      <c r="H63">
+        <f t="shared" si="17"/>
+        <v>0.26166666666666666</v>
+      </c>
+      <c r="J63">
+        <f t="shared" si="18"/>
+        <v>0.16289650571025005</v>
+      </c>
+      <c r="K63">
+        <f t="shared" si="19"/>
+        <v>23550</v>
+      </c>
+      <c r="Q63">
+        <f t="shared" si="20"/>
+        <v>5</v>
+      </c>
+      <c r="R63">
+        <f t="shared" si="21"/>
+        <v>23550</v>
+      </c>
+      <c r="T63" s="1"/>
+      <c r="U63" s="1">
+        <f t="shared" si="24"/>
+        <v>23550</v>
+      </c>
+      <c r="V63" s="2">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>6</v>
+      </c>
+      <c r="D64">
+        <v>36121</v>
+      </c>
+      <c r="E64">
+        <f t="shared" si="23"/>
+        <v>60.201666666666668</v>
+      </c>
+      <c r="F64">
+        <f t="shared" si="16"/>
+        <v>4.5577597651317836</v>
+      </c>
+      <c r="G64">
+        <f>(D64-$M$58)/$M$59</f>
+        <v>0.39467777777777779</v>
+      </c>
+      <c r="H64">
+        <f t="shared" si="17"/>
+        <v>0.40134444444444445</v>
+      </c>
+      <c r="J64">
+        <f t="shared" si="18"/>
+        <v>0.25212404267249638</v>
+      </c>
+      <c r="K64">
+        <f t="shared" si="19"/>
+        <v>36121</v>
+      </c>
+      <c r="Q64">
+        <f t="shared" si="20"/>
+        <v>6</v>
+      </c>
+      <c r="R64">
+        <f t="shared" si="21"/>
+        <v>36121</v>
+      </c>
+      <c r="T64" s="1"/>
+      <c r="U64" s="1">
+        <f t="shared" si="24"/>
+        <v>36121</v>
+      </c>
+      <c r="V64" s="2">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>7</v>
+      </c>
+      <c r="D65">
+        <v>51487</v>
+      </c>
+      <c r="E65">
+        <f t="shared" si="23"/>
+        <v>85.811666666666667</v>
+      </c>
+      <c r="F65">
+        <f t="shared" si="16"/>
+        <v>4.7116975874690565</v>
+      </c>
+      <c r="G65">
+        <f>(D65-$M$58)/$M$59</f>
+        <v>0.56541111111111109</v>
+      </c>
+      <c r="H65">
+        <f t="shared" si="17"/>
+        <v>0.5720777777777778</v>
+      </c>
+      <c r="J65">
+        <f t="shared" si="18"/>
+        <v>0.36119017368529388</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="19"/>
+        <v>51487</v>
+      </c>
+      <c r="Q65">
+        <f t="shared" si="20"/>
+        <v>7</v>
+      </c>
+      <c r="R65">
+        <f t="shared" si="21"/>
+        <v>51487</v>
+      </c>
+      <c r="T65" s="1"/>
+      <c r="U65" s="1">
+        <f t="shared" si="24"/>
+        <v>51487</v>
+      </c>
+      <c r="V65" s="2">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>8</v>
+      </c>
+      <c r="D66">
+        <v>69646</v>
+      </c>
+      <c r="E66">
+        <f t="shared" si="23"/>
+        <v>116.07666666666667</v>
+      </c>
+      <c r="F66">
+        <f t="shared" si="16"/>
+        <v>4.8428961785085454</v>
+      </c>
+      <c r="G66">
+        <f>(D66-$M$58)/$M$59</f>
+        <v>0.76717777777777774</v>
+      </c>
+      <c r="H66">
+        <f t="shared" si="17"/>
+        <v>0.77384444444444445</v>
+      </c>
+      <c r="J66">
+        <f t="shared" si="18"/>
+        <v>0.49008070297472445</v>
+      </c>
+      <c r="K66">
+        <f t="shared" si="19"/>
+        <v>69646</v>
+      </c>
+      <c r="Q66">
+        <f t="shared" si="20"/>
+        <v>8</v>
+      </c>
+      <c r="R66">
+        <f t="shared" si="21"/>
+        <v>69646</v>
+      </c>
+      <c r="T66" s="1"/>
+      <c r="U66" s="1">
+        <f t="shared" si="24"/>
+        <v>69646</v>
+      </c>
+      <c r="V66" s="2">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>9</v>
+      </c>
+      <c r="D67">
+        <v>90600</v>
+      </c>
+      <c r="E67">
+        <f t="shared" si="23"/>
+        <v>151</v>
+      </c>
+      <c r="F67">
+        <f t="shared" si="16"/>
+        <v>4.9571281976768127</v>
+      </c>
+      <c r="G67">
+        <f>(D67-$M$58)/$M$59</f>
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <f t="shared" si="17"/>
+        <v>1.0066666666666666</v>
+      </c>
+      <c r="J67">
+        <f t="shared" si="18"/>
+        <v>0.63880982631470606</v>
+      </c>
+      <c r="K67">
+        <f t="shared" si="19"/>
+        <v>90600</v>
+      </c>
+      <c r="Q67">
+        <f t="shared" si="20"/>
+        <v>9</v>
+      </c>
+      <c r="R67">
+        <f t="shared" si="21"/>
+        <v>90600</v>
+      </c>
+      <c r="T67" s="1"/>
+      <c r="U67" s="1">
+        <f t="shared" si="24"/>
+        <v>90600</v>
+      </c>
+      <c r="V67" s="2">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>10</v>
+      </c>
+      <c r="D68">
+        <v>114346</v>
+      </c>
+      <c r="E68">
+        <f>D68/$D$59</f>
+        <v>190.57666666666665</v>
+      </c>
+      <c r="F68">
+        <f t="shared" si="16"/>
+        <v>5.0582209769155542</v>
+      </c>
+      <c r="G68">
+        <f>(D68-$M$58)/$M$59</f>
+        <v>1.2638444444444445</v>
+      </c>
+      <c r="H68">
+        <f t="shared" si="17"/>
+        <v>1.2705111111111111</v>
+      </c>
+      <c r="J68">
+        <f t="shared" si="18"/>
+        <v>0.80735625004436185</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="19"/>
+        <v>114346.00000000001</v>
+      </c>
+      <c r="Q68">
+        <f t="shared" si="20"/>
+        <v>10</v>
+      </c>
+      <c r="R68">
+        <f t="shared" si="21"/>
+        <v>114346</v>
+      </c>
+      <c r="T68" s="1"/>
+      <c r="U68" s="1">
+        <f t="shared" si="24"/>
+        <v>114346</v>
+      </c>
+      <c r="V68" s="2">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>11</v>
+      </c>
+      <c r="D69">
+        <v>140887</v>
+      </c>
+      <c r="E69">
+        <f t="shared" si="23"/>
+        <v>234.81166666666667</v>
+      </c>
+      <c r="F69">
+        <f t="shared" si="16"/>
+        <v>5.1488709215072683</v>
+      </c>
+      <c r="G69">
+        <f>(D69-$M$58)/$M$59</f>
+        <v>1.5587444444444445</v>
+      </c>
+      <c r="H69">
+        <f t="shared" si="17"/>
+        <v>1.5654111111111111</v>
+      </c>
+      <c r="J69">
+        <f t="shared" si="18"/>
+        <v>0.99574126782456862</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="19"/>
+        <v>140887</v>
+      </c>
+      <c r="Q69">
+        <f t="shared" si="20"/>
+        <v>11</v>
+      </c>
+      <c r="R69">
+        <f t="shared" si="21"/>
+        <v>140887</v>
+      </c>
+      <c r="T69" s="1"/>
+      <c r="U69" s="1">
+        <f t="shared" si="24"/>
+        <v>140887</v>
+      </c>
+      <c r="V69" s="2">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>12</v>
+      </c>
+      <c r="D70">
+        <f>M59*2</f>
+        <v>180000</v>
+      </c>
+      <c r="E70">
+        <f t="shared" si="23"/>
+        <v>300</v>
+      </c>
+      <c r="F70">
+        <f t="shared" si="16"/>
+        <v>5.2552725051033065</v>
+      </c>
+      <c r="G70">
+        <f>(D70-$M$58)/$M$59</f>
+        <v>1.9933333333333334</v>
+      </c>
+      <c r="H70">
+        <f t="shared" si="17"/>
+        <v>2</v>
+      </c>
+      <c r="J70">
+        <f t="shared" si="18"/>
+        <v>1.2733609204539809</v>
+      </c>
+      <c r="K70">
+        <f t="shared" si="19"/>
+        <v>180000</v>
+      </c>
+      <c r="Q70">
+        <f t="shared" si="20"/>
+        <v>12</v>
+      </c>
+      <c r="T70" s="1"/>
+      <c r="U70" s="1">
+        <f t="shared" si="24"/>
+        <v>170221</v>
+      </c>
+      <c r="V70" s="2">
+        <f t="shared" si="22"/>
+        <v>170221</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>50</v>
+      </c>
+      <c r="C72" t="s">
+        <v>51</v>
+      </c>
+      <c r="D72" t="s">
+        <v>52</v>
+      </c>
+      <c r="L72" t="s">
+        <v>53</v>
+      </c>
+      <c r="M72">
+        <v>450</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>1</v>
+      </c>
+      <c r="R72" t="s">
+        <v>0</v>
+      </c>
+      <c r="S72" t="s">
+        <v>55</v>
+      </c>
+      <c r="T72" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>1</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>450</v>
+      </c>
+      <c r="F73">
+        <f>LOG10(D73)</f>
+        <v>2.6532125137753435</v>
+      </c>
+      <c r="G73">
+        <f>(D73-$M$72)/$M$73</f>
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <f>D73/$M$73</f>
+        <v>2.2499999999999998E-3</v>
+      </c>
+      <c r="J73">
+        <f>(D73-$D$73)/$D$83</f>
+        <v>0</v>
+      </c>
+      <c r="L73" t="s">
+        <v>54</v>
+      </c>
+      <c r="M73">
+        <v>200000</v>
+      </c>
+      <c r="N73">
+        <f>M73/M72</f>
+        <v>444.44444444444446</v>
+      </c>
+      <c r="Q73">
+        <f>A73</f>
+        <v>1</v>
+      </c>
+      <c r="R73">
+        <f>D73</f>
+        <v>450</v>
+      </c>
+      <c r="S73">
+        <f>M72</f>
+        <v>450</v>
+      </c>
+      <c r="T73" s="1">
+        <f>M73</f>
+        <v>200000</v>
+      </c>
+      <c r="U73" s="1">
+        <f>R73</f>
+        <v>450</v>
+      </c>
+      <c r="V73" s="2">
+        <f>U73-R73</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>2</v>
+      </c>
+      <c r="D74">
+        <v>4017</v>
+      </c>
+      <c r="E74">
+        <f>D74/$D$59</f>
+        <v>6.6950000000000003</v>
+      </c>
+      <c r="F74">
+        <f t="shared" ref="F74:F84" si="25">LOG10(D74)</f>
+        <v>3.6039018317316716</v>
+      </c>
+      <c r="G74">
+        <f t="shared" ref="G74:G84" si="26">(D74-$M$72)/$M$73</f>
+        <v>1.7835E-2</v>
+      </c>
+      <c r="H74">
+        <f t="shared" ref="H74:H84" si="27">D74/$M$73</f>
+        <v>2.0084999999999999E-2</v>
+      </c>
+      <c r="J74">
+        <f t="shared" ref="J74:J84" si="28">(D74-$D$73)/$D$83</f>
+        <v>1.1407245375700361E-2</v>
+      </c>
+      <c r="Q74">
+        <f t="shared" ref="Q74:Q83" si="29">A74</f>
+        <v>2</v>
+      </c>
+      <c r="R74">
+        <f t="shared" ref="R74:R83" si="30">D74</f>
+        <v>4017</v>
+      </c>
+      <c r="T74" s="1"/>
+      <c r="U74" s="1">
+        <f>ROUNDDOWN(2*$S$73+(Q74-1)^2/64*($T$73-$S$73),0)</f>
+        <v>4017</v>
+      </c>
+      <c r="V74" s="2">
+        <f t="shared" ref="V74:V84" si="31">U74-R74</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>3</v>
+      </c>
+      <c r="D75">
+        <v>13371</v>
+      </c>
+      <c r="E75">
+        <f t="shared" ref="E75:E84" si="32">D75/$D$59</f>
+        <v>22.285</v>
+      </c>
+      <c r="F75">
+        <f t="shared" si="25"/>
+        <v>4.1261638888058387</v>
+      </c>
+      <c r="G75">
+        <f t="shared" si="26"/>
+        <v>6.4604999999999996E-2</v>
+      </c>
+      <c r="H75">
+        <f t="shared" si="27"/>
+        <v>6.6854999999999998E-2</v>
+      </c>
+      <c r="J75">
+        <f t="shared" si="28"/>
+        <v>4.1321283291119809E-2</v>
+      </c>
+      <c r="Q75">
+        <f t="shared" si="29"/>
+        <v>3</v>
+      </c>
+      <c r="R75">
+        <f t="shared" si="30"/>
+        <v>13371</v>
+      </c>
+      <c r="T75" s="1"/>
+      <c r="U75" s="1">
+        <f t="shared" ref="U75:U84" si="33">ROUNDDOWN(2*$S$73+(Q75-1)^2/64*($T$73-$S$73),0)</f>
+        <v>13371</v>
+      </c>
+      <c r="V75" s="2">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>4</v>
+      </c>
+      <c r="D76">
+        <v>28961</v>
+      </c>
+      <c r="E76">
+        <f t="shared" si="32"/>
+        <v>48.268333333333331</v>
+      </c>
+      <c r="F76">
+        <f t="shared" si="25"/>
+        <v>4.46181355362262</v>
+      </c>
+      <c r="G76">
+        <f t="shared" si="26"/>
+        <v>0.14255499999999999</v>
+      </c>
+      <c r="H76">
+        <f t="shared" si="27"/>
+        <v>0.14480499999999999</v>
+      </c>
+      <c r="J76">
+        <f t="shared" si="28"/>
+        <v>9.1178013150152226E-2</v>
+      </c>
+      <c r="Q76">
+        <f t="shared" si="29"/>
+        <v>4</v>
+      </c>
+      <c r="R76">
+        <f t="shared" si="30"/>
+        <v>28961</v>
+      </c>
+      <c r="T76" s="1"/>
+      <c r="U76" s="1">
+        <f t="shared" si="33"/>
+        <v>28961</v>
+      </c>
+      <c r="V76" s="2">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>5</v>
+      </c>
+      <c r="D77">
+        <v>50787</v>
+      </c>
+      <c r="E77">
+        <f t="shared" si="32"/>
+        <v>84.644999999999996</v>
+      </c>
+      <c r="F77">
+        <f t="shared" si="25"/>
+        <v>4.7057525597093663</v>
+      </c>
+      <c r="G77">
+        <f t="shared" si="26"/>
+        <v>0.25168499999999999</v>
+      </c>
+      <c r="H77">
+        <f t="shared" si="27"/>
+        <v>0.25393500000000002</v>
+      </c>
+      <c r="J77">
+        <f t="shared" si="28"/>
+        <v>0.16097743495279759</v>
+      </c>
+      <c r="Q77">
+        <f t="shared" si="29"/>
+        <v>5</v>
+      </c>
+      <c r="R77">
+        <f t="shared" si="30"/>
+        <v>50787</v>
+      </c>
+      <c r="T77" s="1"/>
+      <c r="U77" s="1">
+        <f t="shared" si="33"/>
+        <v>50787</v>
+      </c>
+      <c r="V77" s="2">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>6</v>
+      </c>
+      <c r="D78">
+        <v>78849</v>
+      </c>
+      <c r="E78">
+        <f t="shared" si="32"/>
+        <v>131.41499999999999</v>
+      </c>
+      <c r="F78">
+        <f t="shared" si="25"/>
+        <v>4.8967961897735348</v>
+      </c>
+      <c r="G78">
+        <f t="shared" si="26"/>
+        <v>0.39199499999999998</v>
+      </c>
+      <c r="H78">
+        <f t="shared" si="27"/>
+        <v>0.39424500000000001</v>
+      </c>
+      <c r="J78">
+        <f t="shared" si="28"/>
+        <v>0.25071954869905594</v>
+      </c>
+      <c r="Q78">
+        <f t="shared" si="29"/>
+        <v>6</v>
+      </c>
+      <c r="R78">
+        <f t="shared" si="30"/>
+        <v>78849</v>
+      </c>
+      <c r="T78" s="1"/>
+      <c r="U78" s="1">
+        <f t="shared" si="33"/>
+        <v>78849</v>
+      </c>
+      <c r="V78" s="2">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>7</v>
+      </c>
+      <c r="D79">
+        <v>113146</v>
+      </c>
+      <c r="E79">
+        <f t="shared" si="32"/>
+        <v>188.57666666666665</v>
+      </c>
+      <c r="F79">
+        <f t="shared" si="25"/>
+        <v>5.0536392051432966</v>
+      </c>
+      <c r="G79">
+        <f t="shared" si="26"/>
+        <v>0.56347999999999998</v>
+      </c>
+      <c r="H79">
+        <f t="shared" si="27"/>
+        <v>0.56572999999999996</v>
+      </c>
+      <c r="J79">
+        <f t="shared" si="28"/>
+        <v>0.36040115639470927</v>
+      </c>
+      <c r="Q79">
+        <f t="shared" si="29"/>
+        <v>7</v>
+      </c>
+      <c r="R79">
+        <f t="shared" si="30"/>
+        <v>113146</v>
+      </c>
+      <c r="T79" s="1"/>
+      <c r="U79" s="1">
+        <f t="shared" si="33"/>
+        <v>113146</v>
+      </c>
+      <c r="V79" s="2">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>8</v>
+      </c>
+      <c r="D80">
+        <v>153680</v>
+      </c>
+      <c r="E80">
+        <f t="shared" si="32"/>
+        <v>256.13333333333333</v>
+      </c>
+      <c r="F80">
+        <f t="shared" si="25"/>
+        <v>5.1866173518536369</v>
+      </c>
+      <c r="G80">
+        <f t="shared" si="26"/>
+        <v>0.76615</v>
+      </c>
+      <c r="H80">
+        <f t="shared" si="27"/>
+        <v>0.76839999999999997</v>
+      </c>
+      <c r="J80">
+        <f t="shared" si="28"/>
+        <v>0.49002865402819351</v>
+      </c>
+      <c r="Q80">
+        <f t="shared" si="29"/>
+        <v>8</v>
+      </c>
+      <c r="R80">
+        <f t="shared" si="30"/>
+        <v>153680</v>
+      </c>
+      <c r="T80" s="1"/>
+      <c r="U80" s="1">
+        <f t="shared" si="33"/>
+        <v>153680</v>
+      </c>
+      <c r="V80" s="2">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>9</v>
+      </c>
+      <c r="D81">
+        <v>200450</v>
+      </c>
+      <c r="E81">
+        <f t="shared" si="32"/>
+        <v>334.08333333333331</v>
+      </c>
+      <c r="F81">
+        <f t="shared" si="25"/>
+        <v>5.3020060605865407</v>
+      </c>
+      <c r="G81">
+        <f t="shared" si="26"/>
+        <v>1</v>
+      </c>
+      <c r="H81">
+        <f t="shared" si="27"/>
+        <v>1.0022500000000001</v>
+      </c>
+      <c r="J81">
+        <f t="shared" si="28"/>
+        <v>0.63959884360529073</v>
+      </c>
+      <c r="Q81">
+        <f t="shared" si="29"/>
+        <v>9</v>
+      </c>
+      <c r="R81">
+        <f t="shared" si="30"/>
+        <v>200450</v>
+      </c>
+      <c r="T81" s="1"/>
+      <c r="U81" s="1">
+        <f t="shared" si="33"/>
+        <v>200450</v>
+      </c>
+      <c r="V81" s="2">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>10</v>
+      </c>
+      <c r="D82">
+        <v>253455</v>
+      </c>
+      <c r="E82">
+        <f>D82/$D$59</f>
+        <v>422.42500000000001</v>
+      </c>
+      <c r="F82">
+        <f t="shared" si="25"/>
+        <v>5.4039008631308967</v>
+      </c>
+      <c r="G82">
+        <f t="shared" si="26"/>
+        <v>1.2650250000000001</v>
+      </c>
+      <c r="H82">
+        <f t="shared" si="27"/>
+        <v>1.2672749999999999</v>
+      </c>
+      <c r="J82">
+        <f t="shared" si="28"/>
+        <v>0.80910852713178294</v>
+      </c>
+      <c r="Q82">
+        <f t="shared" si="29"/>
+        <v>10</v>
+      </c>
+      <c r="R82">
+        <f t="shared" si="30"/>
+        <v>253455</v>
+      </c>
+      <c r="T82" s="1"/>
+      <c r="U82" s="1">
+        <f t="shared" si="33"/>
+        <v>253455</v>
+      </c>
+      <c r="V82" s="2">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>11</v>
+      </c>
+      <c r="D83">
+        <v>312696</v>
+      </c>
+      <c r="E83">
+        <f t="shared" si="32"/>
+        <v>521.16</v>
+      </c>
+      <c r="F83">
+        <f t="shared" si="25"/>
+        <v>5.4951223257934974</v>
+      </c>
+      <c r="G83">
+        <f t="shared" si="26"/>
+        <v>1.5612299999999999</v>
+      </c>
+      <c r="H83">
+        <f t="shared" si="27"/>
+        <v>1.56348</v>
+      </c>
+      <c r="J83">
+        <f t="shared" si="28"/>
+        <v>0.99856090260188812</v>
+      </c>
+      <c r="Q83">
+        <f t="shared" si="29"/>
+        <v>11</v>
+      </c>
+      <c r="R83">
+        <f t="shared" si="30"/>
+        <v>312696</v>
+      </c>
+      <c r="T83" s="1"/>
+      <c r="U83" s="1">
+        <f t="shared" si="33"/>
+        <v>312696</v>
+      </c>
+      <c r="V83" s="2">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>12</v>
+      </c>
+      <c r="D84">
+        <f>2*M73</f>
+        <v>400000</v>
+      </c>
+      <c r="E84">
+        <f t="shared" si="32"/>
+        <v>666.66666666666663</v>
+      </c>
+      <c r="F84">
+        <f t="shared" si="25"/>
+        <v>5.6020599913279625</v>
+      </c>
+      <c r="G84">
+        <f t="shared" si="26"/>
+        <v>1.9977499999999999</v>
+      </c>
+      <c r="H84">
+        <f t="shared" si="27"/>
+        <v>2</v>
+      </c>
+      <c r="J84">
+        <f t="shared" si="28"/>
+        <v>1.2777585898124697</v>
+      </c>
+      <c r="Q84">
+        <v>12</v>
+      </c>
+      <c r="U84" s="1">
+        <f t="shared" si="33"/>
+        <v>378174</v>
+      </c>
+      <c r="V84" s="2">
+        <f t="shared" si="31"/>
+        <v>378174</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>50</v>
+      </c>
+      <c r="C86" t="s">
+        <v>51</v>
+      </c>
+      <c r="D86" t="s">
+        <v>52</v>
+      </c>
+      <c r="L86" t="s">
+        <v>53</v>
+      </c>
+      <c r="M86">
+        <v>400</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>1</v>
+      </c>
+      <c r="R86" t="s">
+        <v>0</v>
+      </c>
+      <c r="S86" t="s">
+        <v>55</v>
+      </c>
+      <c r="T86" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>1</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <v>400</v>
+      </c>
+      <c r="F87">
+        <f>LOG10(D87)</f>
+        <v>2.6020599913279625</v>
+      </c>
+      <c r="G87">
+        <f>(D87-$M$72)/$M$73</f>
+        <v>-2.5000000000000001E-4</v>
+      </c>
+      <c r="H87">
+        <f>D87/$M$73</f>
+        <v>2E-3</v>
+      </c>
+      <c r="J87">
+        <f>(D87-$D$73)/$D$83</f>
+        <v>-1.5989971090132269E-4</v>
+      </c>
+      <c r="L87" t="s">
+        <v>54</v>
+      </c>
+      <c r="M87">
+        <v>80000</v>
+      </c>
+      <c r="N87">
+        <f>M87/M86</f>
+        <v>200</v>
+      </c>
+      <c r="Q87">
+        <f>A87</f>
+        <v>1</v>
+      </c>
+      <c r="R87">
+        <f>D87</f>
+        <v>400</v>
+      </c>
+      <c r="S87">
+        <f>M86</f>
+        <v>400</v>
+      </c>
+      <c r="T87" s="1">
+        <f>M87</f>
+        <v>80000</v>
+      </c>
+      <c r="U87" s="1">
+        <f>R87</f>
+        <v>400</v>
+      </c>
+      <c r="V87" s="2">
+        <f>U87-R87</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>2</v>
+      </c>
+      <c r="D88">
+        <v>2043</v>
+      </c>
+      <c r="E88">
+        <f>D88/$D$59</f>
+        <v>3.4049999999999998</v>
+      </c>
+      <c r="F88">
+        <f t="shared" ref="F88:F98" si="34">LOG10(D88)</f>
+        <v>3.3102683666324477</v>
+      </c>
+      <c r="G88">
+        <f t="shared" ref="G88:G98" si="35">(D88-$M$72)/$M$73</f>
+        <v>7.9649999999999999E-3</v>
+      </c>
+      <c r="H88">
+        <f t="shared" ref="H88:H98" si="36">D88/$M$73</f>
+        <v>1.0215E-2</v>
+      </c>
+      <c r="J88">
+        <f t="shared" ref="J88:J98" si="37">(D88-$D$73)/$D$83</f>
+        <v>5.0944047893161405E-3</v>
+      </c>
+      <c r="Q88">
+        <f t="shared" ref="Q88:Q97" si="38">A88</f>
+        <v>2</v>
+      </c>
+      <c r="R88">
+        <f t="shared" ref="R88:R97" si="39">D88</f>
+        <v>2043</v>
+      </c>
+      <c r="T88" s="1"/>
+      <c r="U88" s="1">
+        <f>ROUNDDOWN(2*$S$87+(Q88-1)^2/64*($T$87-$S$87),0)</f>
+        <v>2043</v>
+      </c>
+      <c r="V88" s="2">
+        <f t="shared" ref="V88:V98" si="40">U88-R88</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>3</v>
+      </c>
+      <c r="D89">
+        <v>5775</v>
+      </c>
+      <c r="E89">
+        <f t="shared" ref="E89:E98" si="41">D89/$D$59</f>
+        <v>9.625</v>
+      </c>
+      <c r="F89">
+        <f t="shared" si="34"/>
+        <v>3.7615519885641819</v>
+      </c>
+      <c r="G89">
+        <f t="shared" si="35"/>
+        <v>2.6624999999999999E-2</v>
+      </c>
+      <c r="H89">
+        <f t="shared" si="36"/>
+        <v>2.8875000000000001E-2</v>
+      </c>
+      <c r="J89">
+        <f t="shared" si="37"/>
+        <v>1.7029319210990868E-2</v>
+      </c>
+      <c r="Q89">
+        <f t="shared" si="38"/>
+        <v>3</v>
+      </c>
+      <c r="R89">
+        <f t="shared" si="39"/>
+        <v>5775</v>
+      </c>
+      <c r="T89" s="1"/>
+      <c r="U89" s="1">
+        <f t="shared" ref="U89:U98" si="42">ROUNDDOWN(2*$S$87+(Q89-1)^2/64*($T$87-$S$87),0)</f>
+        <v>5775</v>
+      </c>
+      <c r="V89" s="2">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>4</v>
+      </c>
+      <c r="D90">
+        <v>11993</v>
+      </c>
+      <c r="E90">
+        <f t="shared" si="41"/>
+        <v>19.988333333333333</v>
+      </c>
+      <c r="F90">
+        <f t="shared" si="34"/>
+        <v>4.0789278336807193</v>
+      </c>
+      <c r="G90">
+        <f t="shared" si="35"/>
+        <v>5.7715000000000002E-2</v>
+      </c>
+      <c r="H90">
+        <f t="shared" si="36"/>
+        <v>5.9964999999999997E-2</v>
+      </c>
+      <c r="J90">
+        <f t="shared" si="37"/>
+        <v>3.6914447258679359E-2</v>
+      </c>
+      <c r="Q90">
+        <f t="shared" si="38"/>
+        <v>4</v>
+      </c>
+      <c r="R90">
+        <f t="shared" si="39"/>
+        <v>11993</v>
+      </c>
+      <c r="T90" s="1"/>
+      <c r="U90" s="1">
+        <f t="shared" si="42"/>
+        <v>11993</v>
+      </c>
+      <c r="V90" s="2">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>5</v>
+      </c>
+      <c r="D91">
+        <v>20700</v>
+      </c>
+      <c r="E91">
+        <f t="shared" si="41"/>
+        <v>34.5</v>
+      </c>
+      <c r="F91">
+        <f t="shared" si="34"/>
+        <v>4.3159703454569174</v>
+      </c>
+      <c r="G91">
+        <f t="shared" si="35"/>
+        <v>0.10125000000000001</v>
+      </c>
+      <c r="H91">
+        <f t="shared" si="36"/>
+        <v>0.10349999999999999</v>
+      </c>
+      <c r="J91">
+        <f t="shared" si="37"/>
+        <v>6.475938291503569E-2</v>
+      </c>
+      <c r="Q91">
+        <f t="shared" si="38"/>
+        <v>5</v>
+      </c>
+      <c r="R91">
+        <f t="shared" si="39"/>
+        <v>20700</v>
+      </c>
+      <c r="T91" s="1"/>
+      <c r="U91" s="1">
+        <f t="shared" si="42"/>
+        <v>20700</v>
+      </c>
+      <c r="V91" s="2">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>6</v>
+      </c>
+      <c r="D92">
+        <v>31893</v>
+      </c>
+      <c r="E92">
+        <f t="shared" si="41"/>
+        <v>53.155000000000001</v>
+      </c>
+      <c r="F92">
+        <f t="shared" si="34"/>
+        <v>4.5036953728699967</v>
+      </c>
+      <c r="G92">
+        <f t="shared" si="35"/>
+        <v>0.15721499999999999</v>
+      </c>
+      <c r="H92">
+        <f t="shared" si="36"/>
+        <v>0.159465</v>
+      </c>
+      <c r="J92">
+        <f t="shared" si="37"/>
+        <v>0.10055453219740579</v>
+      </c>
+      <c r="Q92">
+        <f t="shared" si="38"/>
+        <v>6</v>
+      </c>
+      <c r="R92">
+        <f t="shared" si="39"/>
+        <v>31893</v>
+      </c>
+      <c r="T92" s="1"/>
+      <c r="U92" s="1">
+        <f t="shared" si="42"/>
+        <v>31893</v>
+      </c>
+      <c r="V92" s="2">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>7</v>
+      </c>
+      <c r="D93">
+        <v>45575</v>
+      </c>
+      <c r="E93">
+        <f t="shared" si="41"/>
+        <v>75.958333333333329</v>
+      </c>
+      <c r="F93">
+        <f t="shared" si="34"/>
+        <v>4.6587266773270137</v>
+      </c>
+      <c r="G93">
+        <f t="shared" si="35"/>
+        <v>0.22562499999999999</v>
+      </c>
+      <c r="H93">
+        <f t="shared" si="36"/>
+        <v>0.22787499999999999</v>
+      </c>
+      <c r="J93">
+        <f t="shared" si="37"/>
+        <v>0.14430948908844374</v>
+      </c>
+      <c r="Q93">
+        <f t="shared" si="38"/>
+        <v>7</v>
+      </c>
+      <c r="R93">
+        <f t="shared" si="39"/>
+        <v>45575</v>
+      </c>
+      <c r="T93" s="1"/>
+      <c r="U93" s="1">
+        <f t="shared" si="42"/>
+        <v>45575</v>
+      </c>
+      <c r="V93" s="2">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>8</v>
+      </c>
+      <c r="D94">
+        <v>61743</v>
+      </c>
+      <c r="E94">
+        <f t="shared" si="41"/>
+        <v>102.905</v>
+      </c>
+      <c r="F94">
+        <f t="shared" si="34"/>
+        <v>4.790587727377897</v>
+      </c>
+      <c r="G94">
+        <f t="shared" si="35"/>
+        <v>0.30646499999999999</v>
+      </c>
+      <c r="H94">
+        <f t="shared" si="36"/>
+        <v>0.30871500000000002</v>
+      </c>
+      <c r="J94">
+        <f t="shared" si="37"/>
+        <v>0.19601465960549544</v>
+      </c>
+      <c r="Q94">
+        <f t="shared" si="38"/>
+        <v>8</v>
+      </c>
+      <c r="R94">
+        <f t="shared" si="39"/>
+        <v>61743</v>
+      </c>
+      <c r="T94" s="1"/>
+      <c r="U94" s="1">
+        <f t="shared" si="42"/>
+        <v>61743</v>
+      </c>
+      <c r="V94" s="2">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>9</v>
+      </c>
+      <c r="D95">
+        <v>80400</v>
+      </c>
+      <c r="E95">
+        <f t="shared" si="41"/>
+        <v>134</v>
+      </c>
+      <c r="F95">
+        <f t="shared" si="34"/>
+        <v>4.9052560487484511</v>
+      </c>
+      <c r="G95">
+        <f t="shared" si="35"/>
+        <v>0.39974999999999999</v>
+      </c>
+      <c r="H95">
+        <f t="shared" si="36"/>
+        <v>0.40200000000000002</v>
+      </c>
+      <c r="J95">
+        <f t="shared" si="37"/>
+        <v>0.25567963773121499</v>
+      </c>
+      <c r="Q95">
+        <f t="shared" si="38"/>
+        <v>9</v>
+      </c>
+      <c r="R95">
+        <f t="shared" si="39"/>
+        <v>80400</v>
+      </c>
+      <c r="T95" s="1"/>
+      <c r="U95" s="1">
+        <f t="shared" si="42"/>
+        <v>80400</v>
+      </c>
+      <c r="V95" s="2">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>10</v>
+      </c>
+      <c r="D96">
+        <v>101543</v>
+      </c>
+      <c r="E96">
+        <f>D96/$D$59</f>
+        <v>169.23833333333334</v>
+      </c>
+      <c r="F96">
+        <f t="shared" si="34"/>
+        <v>5.0066499901125026</v>
+      </c>
+      <c r="G96">
+        <f t="shared" si="35"/>
+        <v>0.50546500000000005</v>
+      </c>
+      <c r="H96">
+        <f t="shared" si="36"/>
+        <v>0.50771500000000003</v>
+      </c>
+      <c r="J96">
+        <f t="shared" si="37"/>
+        <v>0.3232948294829483</v>
+      </c>
+      <c r="Q96">
+        <f t="shared" si="38"/>
+        <v>10</v>
+      </c>
+      <c r="R96">
+        <f t="shared" si="39"/>
+        <v>101543</v>
+      </c>
+      <c r="T96" s="1"/>
+      <c r="U96" s="1">
+        <f t="shared" si="42"/>
+        <v>101543</v>
+      </c>
+      <c r="V96" s="2">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>11</v>
+      </c>
+      <c r="D97">
+        <v>125175</v>
+      </c>
+      <c r="E97">
+        <f t="shared" si="41"/>
+        <v>208.625</v>
+      </c>
+      <c r="F97">
+        <f t="shared" si="34"/>
+        <v>5.0975176000709466</v>
+      </c>
+      <c r="G97">
+        <f t="shared" si="35"/>
+        <v>0.62362499999999998</v>
+      </c>
+      <c r="H97">
+        <f t="shared" si="36"/>
+        <v>0.62587499999999996</v>
+      </c>
+      <c r="J97">
+        <f t="shared" si="37"/>
+        <v>0.39886982884334943</v>
+      </c>
+      <c r="Q97">
+        <f t="shared" si="38"/>
+        <v>11</v>
+      </c>
+      <c r="R97">
+        <f t="shared" si="39"/>
+        <v>125175</v>
+      </c>
+      <c r="T97" s="1"/>
+      <c r="U97" s="1">
+        <f t="shared" si="42"/>
+        <v>125175</v>
+      </c>
+      <c r="V97" s="2">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>12</v>
+      </c>
+      <c r="E98">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="F98" t="e">
+        <f t="shared" si="34"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="G98">
+        <f t="shared" si="35"/>
+        <v>-2.2499999999999998E-3</v>
+      </c>
+      <c r="H98">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <f t="shared" si="37"/>
+        <v>-1.4390973981119042E-3</v>
+      </c>
+      <c r="Q98">
+        <v>12</v>
+      </c>
+      <c r="U98" s="1">
+        <f t="shared" si="42"/>
+        <v>151293</v>
+      </c>
+      <c r="V98" s="2">
+        <f t="shared" si="40"/>
+        <v>151293</v>
+      </c>
+    </row>
+    <row r="100" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>50</v>
+      </c>
+      <c r="C100" t="s">
+        <v>51</v>
+      </c>
+      <c r="D100" t="s">
+        <v>52</v>
+      </c>
+      <c r="L100" t="s">
+        <v>53</v>
+      </c>
+      <c r="M100">
+        <v>900</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>1</v>
+      </c>
+      <c r="R100" t="s">
+        <v>0</v>
+      </c>
+      <c r="S100" t="s">
+        <v>55</v>
+      </c>
+      <c r="T100" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="101" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>1</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101">
+        <v>900</v>
+      </c>
+      <c r="F101">
+        <f>LOG10(D101)</f>
+        <v>2.9542425094393248</v>
+      </c>
+      <c r="G101">
+        <f>(D101-$M$72)/$M$73</f>
+        <v>2.2499999999999998E-3</v>
+      </c>
+      <c r="H101">
+        <f>D101/$M$73</f>
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="J101">
+        <f>(D101-$D$73)/$D$83</f>
+        <v>1.4390973981119042E-3</v>
+      </c>
+      <c r="L101" t="s">
+        <v>54</v>
+      </c>
+      <c r="M101">
+        <v>370000</v>
+      </c>
+      <c r="N101">
+        <f>M101/M100</f>
+        <v>411.11111111111109</v>
+      </c>
+      <c r="Q101">
+        <f>A101</f>
+        <v>1</v>
+      </c>
+      <c r="R101">
+        <f>D101</f>
+        <v>900</v>
+      </c>
+      <c r="S101">
+        <f>M100</f>
+        <v>900</v>
+      </c>
+      <c r="T101" s="1">
+        <f>M101</f>
+        <v>370000</v>
+      </c>
+      <c r="U101" s="1">
+        <f>R101</f>
+        <v>900</v>
+      </c>
+      <c r="V101" s="2">
+        <f>U101-R101</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>2</v>
+      </c>
+      <c r="D102">
+        <v>7567</v>
+      </c>
+      <c r="E102">
+        <f>D102/$D$59</f>
+        <v>12.611666666666666</v>
+      </c>
+      <c r="F102">
+        <f t="shared" ref="F102:F112" si="43">LOG10(D102)</f>
+        <v>3.8789237339675671</v>
+      </c>
+      <c r="G102">
+        <f t="shared" ref="G102:G112" si="44">(D102-$M$72)/$M$73</f>
+        <v>3.5584999999999999E-2</v>
+      </c>
+      <c r="H102">
+        <f t="shared" ref="H102:H112" si="45">D102/$M$73</f>
+        <v>3.7835000000000001E-2</v>
+      </c>
+      <c r="J102">
+        <f t="shared" ref="J102:J112" si="46">(D102-$D$73)/$D$83</f>
+        <v>2.2760124849694273E-2</v>
+      </c>
+      <c r="Q102">
+        <f t="shared" ref="Q102:Q111" si="47">A102</f>
+        <v>2</v>
+      </c>
+      <c r="R102">
+        <f t="shared" ref="R102:R111" si="48">D102</f>
+        <v>7567</v>
+      </c>
+      <c r="T102" s="1"/>
+      <c r="U102" s="1">
+        <f>ROUNDDOWN(2*$S$101+(Q102-1)^2/64*($T$101-$S$101),0)</f>
+        <v>7567</v>
+      </c>
+      <c r="V102" s="2">
+        <f t="shared" ref="V102:V112" si="49">U102-R102</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>3</v>
+      </c>
+      <c r="D103">
+        <v>24868</v>
+      </c>
+      <c r="E103">
+        <f t="shared" ref="E103:E112" si="50">D103/$D$59</f>
+        <v>41.446666666666665</v>
+      </c>
+      <c r="F103">
+        <f t="shared" si="43"/>
+        <v>4.395640858696118</v>
+      </c>
+      <c r="G103">
+        <f t="shared" si="44"/>
+        <v>0.12209</v>
+      </c>
+      <c r="H103">
+        <f t="shared" si="45"/>
+        <v>0.12434000000000001</v>
+      </c>
+      <c r="J103">
+        <f t="shared" si="46"/>
+        <v>7.8088622815769948E-2</v>
+      </c>
+      <c r="Q103">
+        <f t="shared" si="47"/>
+        <v>3</v>
+      </c>
+      <c r="R103">
+        <f t="shared" si="48"/>
+        <v>24868</v>
+      </c>
+      <c r="T103" s="1"/>
+      <c r="U103" s="1">
+        <f t="shared" ref="U103:U112" si="51">ROUNDDOWN(2*$S$101+(Q103-1)^2/64*($T$101-$S$101),0)</f>
+        <v>24868</v>
+      </c>
+      <c r="V103" s="2">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>4</v>
+      </c>
+      <c r="D104">
+        <v>53704</v>
+      </c>
+      <c r="E104">
+        <f t="shared" si="50"/>
+        <v>89.506666666666661</v>
+      </c>
+      <c r="F104">
+        <f t="shared" si="43"/>
+        <v>4.7300066341768643</v>
+      </c>
+      <c r="G104">
+        <f t="shared" si="44"/>
+        <v>0.26627000000000001</v>
+      </c>
+      <c r="H104">
+        <f t="shared" si="45"/>
+        <v>0.26851999999999998</v>
+      </c>
+      <c r="J104">
+        <f t="shared" si="46"/>
+        <v>0.17030598408678077</v>
+      </c>
+      <c r="Q104">
+        <f t="shared" si="47"/>
+        <v>4</v>
+      </c>
+      <c r="R104">
+        <f t="shared" si="48"/>
+        <v>53704</v>
+      </c>
+      <c r="T104" s="1"/>
+      <c r="U104" s="1">
+        <f t="shared" si="51"/>
+        <v>53704</v>
+      </c>
+      <c r="V104" s="2">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>5</v>
+      </c>
+      <c r="D105">
+        <v>94075</v>
+      </c>
+      <c r="E105">
+        <f t="shared" si="50"/>
+        <v>156.79166666666666</v>
+      </c>
+      <c r="F105">
+        <f t="shared" si="43"/>
+        <v>4.9734742269919021</v>
+      </c>
+      <c r="G105">
+        <f t="shared" si="44"/>
+        <v>0.46812500000000001</v>
+      </c>
+      <c r="H105">
+        <f t="shared" si="45"/>
+        <v>0.47037499999999999</v>
+      </c>
+      <c r="J105">
+        <f t="shared" si="46"/>
+        <v>0.29941220866272672</v>
+      </c>
+      <c r="Q105">
+        <f t="shared" si="47"/>
+        <v>5</v>
+      </c>
+      <c r="R105">
+        <f t="shared" si="48"/>
+        <v>94075</v>
+      </c>
+      <c r="T105" s="1"/>
+      <c r="U105" s="1">
+        <f t="shared" si="51"/>
+        <v>94075</v>
+      </c>
+      <c r="V105" s="2">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>6</v>
+      </c>
+      <c r="D106">
+        <v>145979</v>
+      </c>
+      <c r="E106">
+        <f t="shared" si="50"/>
+        <v>243.29833333333335</v>
+      </c>
+      <c r="F106">
+        <f t="shared" si="43"/>
+        <v>5.1642903842769954</v>
+      </c>
+      <c r="G106">
+        <f t="shared" si="44"/>
+        <v>0.72764499999999999</v>
+      </c>
+      <c r="H106">
+        <f t="shared" si="45"/>
+        <v>0.72989499999999996</v>
+      </c>
+      <c r="J106">
+        <f t="shared" si="46"/>
+        <v>0.4654009005551718</v>
+      </c>
+      <c r="Q106">
+        <f t="shared" si="47"/>
+        <v>6</v>
+      </c>
+      <c r="R106">
+        <f t="shared" si="48"/>
+        <v>145979</v>
+      </c>
+      <c r="T106" s="1"/>
+      <c r="U106" s="1">
+        <f t="shared" si="51"/>
+        <v>145979</v>
+      </c>
+      <c r="V106" s="2">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>7</v>
+      </c>
+      <c r="D107">
+        <v>209418</v>
+      </c>
+      <c r="E107">
+        <f t="shared" si="50"/>
+        <v>349.03</v>
+      </c>
+      <c r="F107">
+        <f t="shared" si="43"/>
+        <v>5.3210140076422805</v>
+      </c>
+      <c r="G107">
+        <f t="shared" si="44"/>
+        <v>1.04484</v>
+      </c>
+      <c r="H107">
+        <f t="shared" si="45"/>
+        <v>1.0470900000000001</v>
+      </c>
+      <c r="J107">
+        <f t="shared" si="46"/>
+        <v>0.66827845575255196</v>
+      </c>
+      <c r="Q107">
+        <f t="shared" si="47"/>
+        <v>7</v>
+      </c>
+      <c r="R107">
+        <f t="shared" si="48"/>
+        <v>209418</v>
+      </c>
+      <c r="T107" s="1"/>
+      <c r="U107" s="1">
+        <f t="shared" si="51"/>
+        <v>209418</v>
+      </c>
+      <c r="V107" s="2">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>8</v>
+      </c>
+      <c r="D108">
+        <v>284392</v>
+      </c>
+      <c r="E108">
+        <f t="shared" si="50"/>
+        <v>473.98666666666668</v>
+      </c>
+      <c r="F108">
+        <f t="shared" si="43"/>
+        <v>5.4539173754447825</v>
+      </c>
+      <c r="G108">
+        <f t="shared" si="44"/>
+        <v>1.41971</v>
+      </c>
+      <c r="H108">
+        <f t="shared" si="45"/>
+        <v>1.4219599999999999</v>
+      </c>
+      <c r="J108">
+        <f t="shared" si="46"/>
+        <v>0.90804487425486735</v>
+      </c>
+      <c r="Q108">
+        <f t="shared" si="47"/>
+        <v>8</v>
+      </c>
+      <c r="R108">
+        <f t="shared" si="48"/>
+        <v>284392</v>
+      </c>
+      <c r="T108" s="1"/>
+      <c r="U108" s="1">
+        <f t="shared" si="51"/>
+        <v>284392</v>
+      </c>
+      <c r="V108" s="2">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>9</v>
+      </c>
+      <c r="D109">
+        <v>370900</v>
+      </c>
+      <c r="E109">
+        <f t="shared" si="50"/>
+        <v>618.16666666666663</v>
+      </c>
+      <c r="F109">
+        <f t="shared" si="43"/>
+        <v>5.5692568333286099</v>
+      </c>
+      <c r="G109">
+        <f t="shared" si="44"/>
+        <v>1.85225</v>
+      </c>
+      <c r="H109">
+        <f t="shared" si="45"/>
+        <v>1.8545</v>
+      </c>
+      <c r="J109">
+        <f t="shared" si="46"/>
+        <v>1.1846969580678999</v>
+      </c>
+      <c r="Q109">
+        <f t="shared" si="47"/>
+        <v>9</v>
+      </c>
+      <c r="R109">
+        <f t="shared" si="48"/>
+        <v>370900</v>
+      </c>
+      <c r="T109" s="1"/>
+      <c r="U109" s="1">
+        <f t="shared" si="51"/>
+        <v>370900</v>
+      </c>
+      <c r="V109" s="2">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>10</v>
+      </c>
+      <c r="D110">
+        <v>468942</v>
+      </c>
+      <c r="E110">
+        <f>D110/$D$59</f>
+        <v>781.57</v>
+      </c>
+      <c r="F110">
+        <f t="shared" si="43"/>
+        <v>5.6711191313342466</v>
+      </c>
+      <c r="G110">
+        <f t="shared" si="44"/>
+        <v>2.34246</v>
+      </c>
+      <c r="H110">
+        <f t="shared" si="45"/>
+        <v>2.3447100000000001</v>
+      </c>
+      <c r="J110">
+        <f t="shared" si="46"/>
+        <v>1.4982347071916493</v>
+      </c>
+      <c r="Q110">
+        <f t="shared" si="47"/>
+        <v>10</v>
+      </c>
+      <c r="R110">
+        <f t="shared" si="48"/>
+        <v>468942</v>
+      </c>
+      <c r="T110" s="1"/>
+      <c r="U110" s="1">
+        <f t="shared" si="51"/>
+        <v>468942</v>
+      </c>
+      <c r="V110" s="2">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>11</v>
+      </c>
+      <c r="D111">
+        <v>578518</v>
+      </c>
+      <c r="E111">
+        <f t="shared" si="50"/>
+        <v>964.19666666666672</v>
+      </c>
+      <c r="F111">
+        <f t="shared" si="43"/>
+        <v>5.7623168761297032</v>
+      </c>
+      <c r="G111">
+        <f t="shared" si="44"/>
+        <v>2.8903400000000001</v>
+      </c>
+      <c r="H111">
+        <f t="shared" si="45"/>
+        <v>2.8925900000000002</v>
+      </c>
+      <c r="J111">
+        <f t="shared" si="46"/>
+        <v>1.8486581216261162</v>
+      </c>
+      <c r="Q111">
+        <f t="shared" si="47"/>
+        <v>11</v>
+      </c>
+      <c r="R111">
+        <f t="shared" si="48"/>
+        <v>578518</v>
+      </c>
+      <c r="T111" s="1"/>
+      <c r="U111" s="1">
+        <f t="shared" si="51"/>
+        <v>578518</v>
+      </c>
+      <c r="V111" s="2">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>12</v>
+      </c>
+      <c r="E112">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="F112" t="e">
+        <f t="shared" si="43"/>
+        <v>#NUM!</v>
+      </c>
+      <c r="G112">
+        <f t="shared" si="44"/>
+        <v>-2.2499999999999998E-3</v>
+      </c>
+      <c r="H112">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <f t="shared" si="46"/>
+        <v>-1.4390973981119042E-3</v>
+      </c>
+      <c r="Q112">
+        <v>12</v>
+      </c>
+      <c r="U112" s="1">
+        <f t="shared" si="51"/>
+        <v>699629</v>
+      </c>
+      <c r="V112" s="2">
+        <f t="shared" si="49"/>
+        <v>699629</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>